--- a/ALCORTA 146/Mayo/MAYO.xlsx
+++ b/ALCORTA 146/Mayo/MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ALCORTA 146\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA60252-FCA3-436B-A4B2-8454B6831EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD05756-2925-4BB7-AE24-DE94CB76C36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Recibo '!$E$6:$N$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$130</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="203">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -585,42 +585,12 @@
     <t>ESTA ES LARROCA</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA PARA MANTENER LAS EXPENSAS</t>
-  </si>
-  <si>
-    <t>Cuota 4</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AYSA </t>
-  </si>
-  <si>
-    <t>Kromacolor compra de pintura - techo 2B</t>
-  </si>
-  <si>
     <t>Aumentados en marz</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados por pago NO informado 5 D</t>
-  </si>
-  <si>
-    <t>Pago ya identificado diciembre</t>
-  </si>
-  <si>
     <t>FERNANDA</t>
   </si>
   <si>
-    <t>Transferencia sin identificar 07/04</t>
-  </si>
-  <si>
-    <t>Pago ya identificado febrero</t>
-  </si>
-  <si>
     <t>Salvatierra Matias -  Desobstruccion de cocina y baño en UF 3D</t>
   </si>
   <si>
@@ -651,10 +621,22 @@
     <t>ARCA MES DE ABRIL</t>
   </si>
   <si>
-    <t>Fumigacion -  ABRIL y MAYO</t>
-  </si>
-  <si>
-    <t>Pago ya identificado ABRIL</t>
+    <t>Cuota 5</t>
+  </si>
+  <si>
+    <t>Debito 07/05</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t>Fumigacion -  MAYO</t>
+  </si>
+  <si>
+    <t>RUSSO</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - ABONO VACACIONES ENCARGADO - ADEUDADAS</t>
   </si>
 </sst>
 </file>
@@ -662,15 +644,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="d/m"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="d/m"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -807,13 +789,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1475,25 +1450,25 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1501,35 +1476,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1539,7 +1514,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1567,19 +1542,19 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1589,83 +1564,66 @@
     <xf numFmtId="16" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1711,10 +1669,10 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1760,7 +1718,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1776,6 +1734,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2141,20 +2102,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M130"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="59"/>
       <c r="B1" s="60" t="s">
         <v>154</v>
@@ -2163,7 +2124,7 @@
       <c r="D1" s="59"/>
       <c r="E1" s="59"/>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="61"/>
       <c r="B2" s="62" t="s">
         <v>149</v>
@@ -2172,7 +2133,7 @@
       <c r="D2" s="63"/>
       <c r="E2" s="64"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="65"/>
       <c r="B3" s="66" t="s">
         <v>48</v>
@@ -2181,7 +2142,7 @@
       <c r="D3" s="66"/>
       <c r="E3" s="67"/>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65"/>
       <c r="B4" s="66" t="s">
         <v>178</v>
@@ -2192,7 +2153,7 @@
       <c r="D4" s="66"/>
       <c r="E4" s="67"/>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="65"/>
       <c r="B5" s="66" t="s">
         <v>179</v>
@@ -2201,12 +2162,12 @@
       <c r="D5" s="66"/>
       <c r="E5" s="67"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="69" t="s">
@@ -2214,14 +2175,14 @@
       </c>
       <c r="E6" s="70"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="65"/>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
       <c r="D7" s="66"/>
       <c r="E7" s="67"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="68" t="s">
         <v>47</v>
       </c>
@@ -2230,142 +2191,142 @@
       <c r="D8" s="69"/>
       <c r="E8" s="70"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="71"/>
       <c r="B9" s="71"/>
       <c r="C9" s="71"/>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="71"/>
       <c r="B10" s="71"/>
       <c r="C10" s="71"/>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="71"/>
       <c r="B11" s="71"/>
       <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="71"/>
       <c r="B12" s="71"/>
       <c r="C12" s="71"/>
       <c r="D12" s="71"/>
       <c r="E12" s="71"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="71"/>
       <c r="B13" s="71"/>
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="71"/>
       <c r="B14" s="71"/>
       <c r="C14" s="71"/>
       <c r="D14" s="71"/>
       <c r="E14" s="71"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="155"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="155"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="155"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
-      <c r="B18" s="155"/>
-      <c r="C18" s="155"/>
-      <c r="D18" s="155"/>
-      <c r="E18" s="155"/>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="146" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="146"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="146"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="146"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="146"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+    </row>
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="71"/>
       <c r="B19" s="71"/>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="71"/>
       <c r="B20" s="71"/>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
     </row>
-    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="71"/>
       <c r="B21" s="71"/>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
     </row>
-    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="156"/>
-      <c r="B22" s="157"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="157"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="157"/>
-      <c r="B24" s="157"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="157"/>
-      <c r="B25" s="157"/>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="157"/>
-      <c r="B26" s="157"/>
-      <c r="C26" s="157"/>
-      <c r="D26" s="157"/>
-      <c r="E26" s="157"/>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="147"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="148"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148"/>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="148"/>
+      <c r="B24" s="148"/>
+      <c r="C24" s="148"/>
+      <c r="D24" s="148"/>
+      <c r="E24" s="148"/>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="148"/>
+      <c r="B25" s="148"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="148"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="71"/>
       <c r="B27" s="71"/>
       <c r="C27" s="71"/>
       <c r="D27" s="71"/>
       <c r="E27" s="71"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="72" t="s">
         <v>34</v>
       </c>
@@ -2374,7 +2335,7 @@
       <c r="D28" s="75"/>
       <c r="E28" s="76"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>118</v>
       </c>
@@ -2383,7 +2344,7 @@
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="77" t="s">
         <v>112</v>
       </c>
@@ -2391,14 +2352,14 @@
         <v>127</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D30" s="79">
         <v>1664921.03</v>
       </c>
       <c r="E30" s="78"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="77"/>
       <c r="B31" s="78" t="s">
         <v>113</v>
@@ -2409,7 +2370,7 @@
       </c>
       <c r="E31" s="78"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="77"/>
       <c r="B32" s="78" t="s">
         <v>146</v>
@@ -2420,35 +2381,35 @@
       </c>
       <c r="E32" s="78"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="78"/>
       <c r="C33" s="78"/>
       <c r="D33" s="80"/>
       <c r="E33" s="78"/>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
       <c r="B34" s="78"/>
       <c r="C34" s="78"/>
       <c r="D34" s="80"/>
       <c r="E34" s="78"/>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
       <c r="B35" s="78"/>
       <c r="C35" s="78"/>
       <c r="D35" s="81"/>
       <c r="E35" s="78"/>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
       <c r="B36" s="78"/>
       <c r="C36" s="78"/>
       <c r="D36" s="81"/>
       <c r="E36" s="78"/>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>1</v>
       </c>
@@ -2460,7 +2421,7 @@
         <v>1302801</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="78" t="s">
         <v>157</v>
       </c>
@@ -2472,7 +2433,7 @@
         <v>235611</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78" t="s">
         <v>156</v>
       </c>
@@ -2485,7 +2446,7 @@
         <v>1067190</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78" t="s">
         <v>146</v>
       </c>
@@ -2494,7 +2455,7 @@
       <c r="D40" s="84"/>
       <c r="E40" s="78"/>
     </row>
-    <row r="41" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
         <v>155</v>
       </c>
@@ -2507,7 +2468,7 @@
       </c>
       <c r="F41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>141</v>
       </c>
@@ -2516,43 +2477,43 @@
       <c r="D42" s="21"/>
       <c r="E42" s="85"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="78" t="s">
         <v>142</v>
       </c>
       <c r="B43" s="78" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C43" s="78"/>
-      <c r="D43" s="153">
+      <c r="D43" s="79">
         <v>28000</v>
       </c>
       <c r="E43" s="86"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="78" t="s">
         <v>143</v>
       </c>
       <c r="B44" s="78" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C44" s="78"/>
-      <c r="D44" s="153">
+      <c r="D44" s="79">
         <v>112000</v>
       </c>
       <c r="E44" s="86"/>
       <c r="G44" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="78"/>
       <c r="B45" s="78"/>
       <c r="C45" s="78"/>
       <c r="D45" s="17"/>
       <c r="E45" s="86"/>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>114</v>
       </c>
@@ -2564,7 +2525,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>2</v>
       </c>
@@ -2573,27 +2534,27 @@
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="77" t="s">
         <v>128</v>
       </c>
       <c r="B48" s="78"/>
       <c r="C48" s="78" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D48" s="17">
         <v>25842</v>
       </c>
       <c r="E48" s="24"/>
     </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="77"/>
       <c r="B49" s="78"/>
       <c r="C49" s="78"/>
       <c r="D49" s="17"/>
       <c r="E49" s="88"/>
     </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
         <v>3</v>
       </c>
@@ -2605,7 +2566,7 @@
         <v>25842</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>115</v>
       </c>
@@ -2614,33 +2575,35 @@
       <c r="D51" s="26"/>
       <c r="E51" s="90"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="78" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
+      <c r="C52" s="78" t="s">
+        <v>198</v>
+      </c>
       <c r="D52" s="17">
-        <v>726324.3</v>
+        <v>776011.89</v>
       </c>
       <c r="E52" s="24"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="78" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B53" s="78" t="s">
         <v>131</v>
       </c>
       <c r="C53" s="78" t="s">
-        <v>187</v>
-      </c>
-      <c r="D53" s="142">
+        <v>199</v>
+      </c>
+      <c r="D53" s="24">
         <v>74921.45</v>
       </c>
       <c r="E53" s="24"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="78" t="str">
         <f>A53</f>
         <v>Sindicatos periodo MAYO</v>
@@ -2650,14 +2613,14 @@
       </c>
       <c r="C54" s="78" t="str">
         <f>C53</f>
-        <v>Debito 14/04</v>
-      </c>
-      <c r="D54" s="152">
+        <v>Debito 12/05</v>
+      </c>
+      <c r="D54" s="17">
         <v>132219.87</v>
       </c>
       <c r="E54" s="24"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="78" t="str">
         <f>A54</f>
         <v>Sindicatos periodo MAYO</v>
@@ -2667,21 +2630,21 @@
       </c>
       <c r="C55" s="78" t="str">
         <f>C54</f>
-        <v>Debito 14/04</v>
-      </c>
-      <c r="D55" s="152">
+        <v>Debito 12/05</v>
+      </c>
+      <c r="D55" s="17">
         <v>8324.7099999999991</v>
       </c>
       <c r="E55" s="88"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="78"/>
       <c r="B56" s="78"/>
       <c r="C56" s="78"/>
       <c r="D56" s="17"/>
       <c r="E56" s="24"/>
     </row>
-    <row r="57" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
         <v>4</v>
       </c>
@@ -2690,10 +2653,10 @@
       <c r="D57" s="27"/>
       <c r="E57" s="91">
         <f>SUM(D52:D56)</f>
-        <v>941790.33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>991477.91999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>117</v>
       </c>
@@ -2702,704 +2665,633 @@
       <c r="D58" s="26"/>
       <c r="E58" s="90"/>
     </row>
-    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="78" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B59" s="92"/>
       <c r="C59" s="78"/>
-      <c r="D59" s="17">
-        <v>472992.23</v>
-      </c>
+      <c r="D59" s="17"/>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="B60" s="92"/>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="92" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="92" t="s">
+        <v>193</v>
+      </c>
       <c r="C60" s="78"/>
       <c r="D60" s="17">
-        <v>524627.71</v>
-      </c>
-      <c r="E60" s="24"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="B61" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="C61" s="78"/>
-      <c r="D61" s="152">
         <v>53800</v>
       </c>
-      <c r="E61" s="17"/>
-    </row>
-    <row r="62" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E60" s="17"/>
+    </row>
+    <row r="61" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="93"/>
+      <c r="C61" s="94"/>
+      <c r="D61" s="17">
+        <v>0</v>
+      </c>
+      <c r="E61" s="24"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="93"/>
+        <v>200</v>
+      </c>
+      <c r="B62" s="78"/>
       <c r="C62" s="94"/>
       <c r="D62" s="17">
-        <v>0</v>
+        <v>45800</v>
       </c>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="78" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="B63" s="78"/>
-      <c r="C63" s="94"/>
-      <c r="D63" s="17">
-        <v>85000</v>
-      </c>
+      <c r="C63" s="78"/>
+      <c r="D63" s="17"/>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="78" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="B64" s="78"/>
       <c r="C64" s="78"/>
       <c r="D64" s="17">
-        <v>21078.1</v>
+        <v>6490.63</v>
       </c>
       <c r="E64" s="24"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="78" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B65" s="78"/>
       <c r="C65" s="78"/>
-      <c r="D65" s="152">
-        <v>7530</v>
-      </c>
-      <c r="E65" s="24"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D65" s="187">
+        <v>96090.5</v>
+      </c>
+      <c r="E65" s="143"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="78" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="B66" s="78"/>
       <c r="C66" s="78"/>
-      <c r="D66" s="150">
-        <v>146134.44</v>
-      </c>
-      <c r="E66" s="147"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="78" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" s="78"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="152">
+      <c r="D66" s="17">
         <v>13653.85</v>
       </c>
-      <c r="E67" s="24"/>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="78"/>
-      <c r="B68" s="95"/>
-      <c r="C68" s="96"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="88"/>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="20" t="s">
+      <c r="E66" s="24"/>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="78"/>
+      <c r="B67" s="95"/>
+      <c r="C67" s="96"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="88"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
         <v>5</v>
+      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="89">
+        <f>SUM(D59:D67)</f>
+        <v>215834.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="25"/>
-      <c r="E69" s="89">
-        <f>SUM(D59:D68)</f>
-        <v>1324816.33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="89"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E69" s="89"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="78" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="17">
+        <v>44595</v>
+      </c>
+      <c r="E70" s="86"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="78" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B71" s="78"/>
       <c r="C71" s="78"/>
       <c r="D71" s="17">
-        <v>44595</v>
-      </c>
-      <c r="E71" s="86"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52084.53</v>
+      </c>
+      <c r="E71" s="24"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="78" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B72" s="78"/>
       <c r="C72" s="78"/>
       <c r="D72" s="17">
-        <v>52084.53</v>
+        <v>45800</v>
       </c>
       <c r="E72" s="24"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="78" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="B73" s="78"/>
       <c r="C73" s="78"/>
-      <c r="D73" s="152">
-        <v>45800</v>
+      <c r="D73" s="24">
+        <v>2350</v>
       </c>
       <c r="E73" s="24"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="78" t="s">
-        <v>150</v>
-      </c>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="78"/>
       <c r="B74" s="78"/>
       <c r="C74" s="78"/>
-      <c r="D74" s="24">
-        <v>2300</v>
-      </c>
-      <c r="E74" s="24"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="78" t="s">
-        <v>191</v>
-      </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="24">
-        <v>98800</v>
-      </c>
-      <c r="E75" s="17"/>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="20" t="s">
+      <c r="D74" s="24"/>
+      <c r="E74" s="17"/>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="97">
-        <f>SUM(D71:D75)</f>
-        <v>243579.53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="19" t="s">
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="97">
+        <f>SUM(D70:D74)</f>
+        <v>144829.53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="89"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="78" t="s">
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="89"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="78" t="s">
         <v>38</v>
       </c>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="17">
+        <f>52561.98+29000</f>
+        <v>81561.98000000001</v>
+      </c>
+      <c r="E77" s="98"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="77"/>
       <c r="B78" s="78"/>
       <c r="C78" s="78"/>
-      <c r="D78" s="17">
-        <f>90714.05</f>
-        <v>90714.05</v>
-      </c>
-      <c r="E78" s="98"/>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="77"/>
-      <c r="B79" s="78"/>
-      <c r="C79" s="78"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="99"/>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="20" t="s">
+      <c r="D78" s="17"/>
+      <c r="E78" s="99"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="89">
-        <f>SUM(D78:D79)</f>
-        <v>90714.05</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="78"/>
-      <c r="B81" s="78"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="78"/>
-      <c r="E81" s="100"/>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="101" t="s">
-        <v>185</v>
-      </c>
-      <c r="B82" s="101"/>
-      <c r="C82" s="101"/>
-      <c r="D82" s="102"/>
-      <c r="E82" s="103">
-        <v>266278.07</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="104"/>
-      <c r="B83" s="71"/>
-      <c r="C83" s="71"/>
-      <c r="D83" s="71"/>
-      <c r="E83" s="105"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="89">
+        <f>SUM(D77:D78)</f>
+        <v>81561.98000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="78"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="100"/>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="101" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="101"/>
+      <c r="C81" s="101"/>
+      <c r="D81" s="102"/>
+      <c r="E81" s="103">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="104"/>
+      <c r="B82" s="71"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="105"/>
+      <c r="F82" s="31"/>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="107"/>
+      <c r="C83" s="108"/>
+      <c r="D83" s="108"/>
+      <c r="E83" s="109">
+        <f>(SUM(E30:E81))</f>
+        <v>4602347.41</v>
+      </c>
       <c r="F83" s="31"/>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="106" t="s">
-        <v>39</v>
-      </c>
-      <c r="B84" s="107"/>
-      <c r="C84" s="108"/>
-      <c r="D84" s="108"/>
-      <c r="E84" s="109">
-        <f>(SUM(E30:E82))</f>
-        <v>4335821.3099999996</v>
-      </c>
-      <c r="F84" s="31"/>
-      <c r="G84" s="31"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G83" s="31"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="71"/>
+      <c r="B84" s="71"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="71"/>
       <c r="B85" s="71"/>
       <c r="C85" s="71"/>
       <c r="D85" s="71"/>
       <c r="E85" s="71"/>
-    </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="71"/>
-      <c r="B86" s="71"/>
-      <c r="C86" s="71"/>
+      <c r="F85" s="31"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="158"/>
+      <c r="C86" s="110"/>
       <c r="D86" s="71"/>
       <c r="E86" s="71"/>
-      <c r="F86" s="31"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="166" t="s">
-        <v>158</v>
-      </c>
-      <c r="B87" s="167"/>
-      <c r="C87" s="110"/>
+    </row>
+    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="149"/>
+      <c r="B87" s="150"/>
+      <c r="C87" s="17"/>
       <c r="D87" s="71"/>
       <c r="E87" s="71"/>
     </row>
-    <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="158" t="s">
-        <v>189</v>
-      </c>
-      <c r="B88" s="159"/>
-      <c r="C88" s="17">
-        <v>35125.78</v>
-      </c>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="151"/>
+      <c r="B88" s="152"/>
+      <c r="C88" s="17"/>
       <c r="D88" s="71"/>
       <c r="E88" s="71"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="160"/>
-      <c r="B89" s="161"/>
-      <c r="C89" s="17"/>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="153"/>
+      <c r="B89" s="154"/>
+      <c r="C89" s="111"/>
       <c r="D89" s="71"/>
-      <c r="E89" s="71"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="162"/>
-      <c r="B90" s="163"/>
-      <c r="C90" s="111"/>
+      <c r="E89" s="112"/>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B90" s="156"/>
+      <c r="C90" s="113">
+        <f>SUM(C87:C89)</f>
+        <v>0</v>
+      </c>
       <c r="D90" s="71"/>
-      <c r="E90" s="112"/>
-    </row>
-    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="164" t="s">
-        <v>16</v>
-      </c>
-      <c r="B91" s="165"/>
-      <c r="C91" s="113">
-        <f>SUM(C88:C90)</f>
-        <v>35125.78</v>
-      </c>
+      <c r="E90" s="71"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="71"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
       <c r="D91" s="71"/>
       <c r="E91" s="71"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="71"/>
-      <c r="B92" s="71"/>
-      <c r="C92" s="71"/>
-      <c r="D92" s="71"/>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="B92" s="114"/>
+      <c r="C92" s="115"/>
+      <c r="D92" s="116"/>
       <c r="E92" s="71"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="114" t="s">
-        <v>163</v>
-      </c>
-      <c r="B93" s="114"/>
-      <c r="C93" s="115"/>
-      <c r="D93" s="116"/>
+    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="71"/>
+      <c r="B93" s="71"/>
+      <c r="C93" s="71"/>
+      <c r="D93" s="71"/>
       <c r="E93" s="71"/>
     </row>
-    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
-      <c r="B94" s="71"/>
+    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="117" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" s="118">
+        <f>E83</f>
+        <v>4602347.41</v>
+      </c>
       <c r="C94" s="71"/>
       <c r="D94" s="71"/>
-      <c r="E94" s="71"/>
-    </row>
-    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="117" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" s="118">
-        <f>E84</f>
-        <v>4335821.3099999996</v>
+      <c r="E94" s="112"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="119" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="120">
+        <f>E83-E81</f>
+        <v>2902347.41</v>
       </c>
       <c r="C95" s="71"/>
       <c r="D95" s="71"/>
-      <c r="E95" s="112"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="119" t="s">
-        <v>41</v>
-      </c>
-      <c r="B96" s="120">
-        <f>E84-E82</f>
-        <v>4069543.2399999998</v>
+      <c r="E95" s="71"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="121" t="s">
+        <v>160</v>
+      </c>
+      <c r="B96" s="122">
+        <f>C90+C92</f>
+        <v>0</v>
       </c>
       <c r="C96" s="71"/>
       <c r="D96" s="71"/>
       <c r="E96" s="71"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B97" s="122">
-        <f>C91+C93</f>
-        <v>35125.78</v>
+        <f>C90</f>
+        <v>0</v>
       </c>
       <c r="C97" s="71"/>
       <c r="D97" s="71"/>
       <c r="E97" s="71"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="121" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B98" s="122">
-        <f>C91</f>
-        <v>35125.78</v>
+        <f>B95+B97</f>
+        <v>2902347.41</v>
       </c>
       <c r="C98" s="71"/>
       <c r="D98" s="71"/>
       <c r="E98" s="71"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="121" t="s">
-        <v>161</v>
-      </c>
-      <c r="B99" s="122">
-        <f>B96+B98</f>
-        <v>4104669.0199999996</v>
-      </c>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="71"/>
+      <c r="B99" s="71"/>
       <c r="C99" s="71"/>
       <c r="D99" s="71"/>
       <c r="E99" s="71"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="71"/>
-      <c r="B100" s="71"/>
-      <c r="C100" s="71"/>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="148"/>
+      <c r="B100" s="148"/>
+      <c r="C100" s="148"/>
       <c r="D100" s="71"/>
       <c r="E100" s="71"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="157"/>
-      <c r="B101" s="157"/>
-      <c r="C101" s="157"/>
+    <row r="101" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="148"/>
+      <c r="B101" s="148"/>
+      <c r="C101" s="148"/>
       <c r="D101" s="71"/>
       <c r="E101" s="71"/>
     </row>
-    <row r="102" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="157"/>
-      <c r="B102" s="157"/>
-      <c r="C102" s="157"/>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="71"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
       <c r="D102" s="71"/>
       <c r="E102" s="71"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="71"/>
-      <c r="B103" s="71"/>
-      <c r="C103" s="71"/>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="B103" s="124"/>
+      <c r="C103" s="125"/>
       <c r="D103" s="71"/>
       <c r="E103" s="71"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="123" t="s">
-        <v>176</v>
-      </c>
-      <c r="B104" s="124"/>
-      <c r="C104" s="125"/>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" s="124">
+        <v>-28063.224127181806</v>
+      </c>
+      <c r="C104" s="126"/>
       <c r="D104" s="71"/>
       <c r="E104" s="71"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B105" s="124">
-        <v>333425.41715271771</v>
-      </c>
-      <c r="C105" s="126"/>
-      <c r="D105" s="71"/>
+    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="127" t="s">
+        <v>44</v>
+      </c>
+      <c r="B105" s="128">
+        <f>PRORRATEO!I44</f>
+        <v>2822724.5812739334</v>
+      </c>
+      <c r="C105" s="125"/>
+      <c r="D105" s="112"/>
       <c r="E105" s="71"/>
     </row>
-    <row r="106" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="B106" s="128">
-        <f>PRORRATEO!I44</f>
-        <v>3730327.6487200996</v>
+    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" s="142">
+        <f>-(B98+B114)</f>
+        <v>-2552386.41</v>
       </c>
       <c r="C106" s="125"/>
-      <c r="D106" s="112"/>
+      <c r="D106" s="71"/>
       <c r="E106" s="71"/>
     </row>
-    <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="129" t="s">
-        <v>208</v>
-      </c>
-      <c r="B107" s="151">
-        <v>-128221</v>
-      </c>
-      <c r="C107" s="125"/>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="B107" s="42">
+        <f>SUM(B104:B106)</f>
+        <v>242274.94714675145</v>
+      </c>
+      <c r="C107" s="131"/>
       <c r="D107" s="112"/>
       <c r="E107" s="71"/>
     </row>
-    <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="129" t="s">
-        <v>196</v>
-      </c>
-      <c r="B108" s="151">
-        <v>-135913.38</v>
-      </c>
-      <c r="C108" s="125"/>
-      <c r="D108" s="112"/>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="71"/>
+      <c r="B108" s="132"/>
+      <c r="C108" s="131"/>
+      <c r="D108" s="71"/>
       <c r="E108" s="71"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="129" t="s">
-        <v>193</v>
-      </c>
-      <c r="B109" s="144">
-        <v>-115500</v>
-      </c>
-      <c r="C109" s="130"/>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="71"/>
+      <c r="B109" s="133"/>
+      <c r="C109" s="131"/>
       <c r="D109" s="71"/>
       <c r="E109" s="71"/>
     </row>
-    <row r="110" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="148" t="s">
-        <v>192</v>
-      </c>
-      <c r="B110" s="146">
-        <v>-12720</v>
-      </c>
-      <c r="C110" s="125"/>
-      <c r="D110" s="71"/>
-      <c r="E110" s="71"/>
-    </row>
-    <row r="111" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="131" t="s">
+    <row r="110" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="71"/>
+      <c r="B110" s="132"/>
+      <c r="C110" s="134"/>
+      <c r="D110" s="135"/>
+      <c r="E110" s="135"/>
+    </row>
+    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="136" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="24"/>
+      <c r="C111" s="134"/>
+      <c r="D111" s="135"/>
+      <c r="E111" s="137"/>
+    </row>
+    <row r="112" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" s="24">
+        <v>331375.87932759989</v>
+      </c>
+      <c r="C112" s="134"/>
+      <c r="D112" s="137"/>
+      <c r="E112" s="137"/>
+    </row>
+    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B113" s="24">
+        <f>PRORRATEO!I45</f>
+        <v>454708.97119825997</v>
+      </c>
+      <c r="C113" s="131"/>
+      <c r="D113" s="112"/>
+      <c r="E113" s="71"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="145">
-        <f>-(B99+B119)</f>
-        <v>-3754758.0199999996</v>
-      </c>
-      <c r="C111" s="125"/>
-      <c r="D111" s="71"/>
-      <c r="E111" s="71"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="132" t="s">
-        <v>16</v>
-      </c>
-      <c r="B112" s="42">
-        <f>SUM(B105:B111)</f>
-        <v>-83359.334127182141</v>
-      </c>
-      <c r="C112" s="133"/>
-      <c r="D112" s="112"/>
-      <c r="E112" s="71"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="71"/>
-      <c r="B113" s="134"/>
-      <c r="C113" s="133"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="71"/>
-      <c r="B114" s="135"/>
-      <c r="C114" s="133"/>
+      <c r="B114" s="41">
+        <f>-(D44+D73+G38)</f>
+        <v>-349961</v>
+      </c>
+      <c r="C114" s="131"/>
       <c r="D114" s="71"/>
       <c r="E114" s="71"/>
     </row>
-    <row r="115" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="71"/>
-      <c r="B115" s="134"/>
-      <c r="C115" s="136"/>
-      <c r="D115" s="137"/>
-      <c r="E115" s="137"/>
-    </row>
-    <row r="116" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="138" t="s">
-        <v>45</v>
-      </c>
-      <c r="B116" s="24"/>
-      <c r="C116" s="136"/>
-      <c r="D116" s="137"/>
-      <c r="E116" s="139"/>
-    </row>
-    <row r="117" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="78" t="s">
-        <v>42</v>
-      </c>
-      <c r="B117" s="24">
-        <v>-29863.384174900071</v>
-      </c>
-      <c r="C117" s="136"/>
-      <c r="D117" s="139"/>
-      <c r="E117" s="139"/>
-    </row>
-    <row r="118" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="78" t="s">
-        <v>35</v>
-      </c>
-      <c r="B118" s="24">
-        <f>PRORRATEO!I45</f>
-        <v>711150.2635024999</v>
-      </c>
-      <c r="C118" s="133"/>
-      <c r="D118" s="112"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="78"/>
+      <c r="B115" s="41"/>
+      <c r="C115" s="131"/>
+      <c r="D115" s="71"/>
+      <c r="E115" s="71"/>
+    </row>
+    <row r="116" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="141"/>
+      <c r="B116" s="140"/>
+      <c r="C116" s="138"/>
+      <c r="D116" s="71"/>
+      <c r="E116" s="71"/>
+    </row>
+    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="141"/>
+      <c r="B117" s="140"/>
+      <c r="C117" s="138"/>
+      <c r="D117" s="71"/>
+      <c r="E117" s="71"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="136" t="s">
+        <v>46</v>
+      </c>
+      <c r="B118" s="42">
+        <f>SUM(B112:B117)</f>
+        <v>436123.85052585986</v>
+      </c>
+      <c r="C118" s="125"/>
+      <c r="D118" s="71"/>
       <c r="E118" s="71"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="B119" s="41">
-        <f>-(D44+D74+G38)</f>
-        <v>-349911</v>
-      </c>
-      <c r="C119" s="133"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="71"/>
+      <c r="B119" s="71"/>
+      <c r="C119" s="71"/>
       <c r="D119" s="71"/>
       <c r="E119" s="71"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="78"/>
-      <c r="B120" s="41"/>
-      <c r="C120" s="133"/>
-      <c r="D120" s="71"/>
-      <c r="E120" s="71"/>
-    </row>
-    <row r="121" spans="1:5" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="143"/>
-      <c r="B121" s="142"/>
-      <c r="C121" s="140"/>
-      <c r="D121" s="71"/>
-      <c r="E121" s="71"/>
-    </row>
-    <row r="122" spans="1:5" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="143"/>
-      <c r="B122" s="142"/>
-      <c r="C122" s="140"/>
-      <c r="D122" s="71"/>
-      <c r="E122" s="71"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="138" t="s">
-        <v>46</v>
-      </c>
-      <c r="B123" s="42">
-        <f>SUM(B117:B122)</f>
-        <v>331375.87932759989</v>
-      </c>
-      <c r="C123" s="125"/>
-      <c r="D123" s="71"/>
-      <c r="E123" s="71"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="71"/>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="154" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="145" t="s">
         <v>164</v>
       </c>
-      <c r="B126" s="154"/>
-      <c r="C126" s="154"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="154"/>
-      <c r="B127" s="154"/>
-      <c r="C127" s="154"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B128" s="1"/>
-      <c r="C128" s="23">
-        <v>131386.79</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="32" t="s">
+      <c r="B121" s="145"/>
+      <c r="C121" s="145"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="145"/>
+      <c r="B122" s="145"/>
+      <c r="C122" s="145"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="23"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B129" s="32"/>
-      <c r="C129" s="33">
-        <f>SUM(C128:C128)</f>
-        <v>131386.79</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M130" s="4"/>
+      <c r="B124" s="32"/>
+      <c r="C124" s="33">
+        <f>SUM(C123:C123)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M125" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A126:C127"/>
+    <mergeCell ref="A121:C122"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="A22:E26"/>
+    <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A101:C102"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A100:C101"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3410,27 +3302,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="5" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3449,7 +3341,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3464,13 +3356,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="39">
-        <v>3957433.496999999</v>
+        <v>2902347.4099999997</v>
       </c>
       <c r="O2" s="39">
-        <v>3957433.497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4602347.41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3486,14 +3378,14 @@
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="170">
-        <f>N2</f>
-        <v>3957433.496999999</v>
-      </c>
-      <c r="O3" s="170"/>
+      <c r="N3" s="161">
+        <f>O2</f>
+        <v>4602347.41</v>
+      </c>
+      <c r="O3" s="161"/>
       <c r="P3" s="5"/>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3509,74 +3401,72 @@
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="169">
-        <v>0</v>
-      </c>
-      <c r="O4" s="169"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="171" t="s">
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="178" t="s">
+      <c r="B5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="180" t="s">
+      <c r="C5" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="180" t="s">
+      <c r="D5" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="180" t="s">
+      <c r="E5" s="171" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="171" t="s">
+      <c r="F5" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="171" t="s">
+      <c r="G5" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="171" t="s">
+      <c r="H5" s="162" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="175" t="s">
+      <c r="J5" s="166" t="s">
         <v>147</v>
       </c>
-      <c r="K5" s="173" t="s">
+      <c r="K5" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="173" t="s">
+      <c r="L5" s="164" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="173" t="s">
+      <c r="M5" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="173" t="s">
+      <c r="N5" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="173" t="s">
+      <c r="O5" s="164" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="172"/>
-      <c r="B6" s="179"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="181"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="172"/>
-      <c r="H6" s="172"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="163"/>
+      <c r="B6" s="170"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="174"/>
-      <c r="L6" s="177"/>
-      <c r="M6" s="177"/>
-      <c r="N6" s="177"/>
-      <c r="O6" s="174"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J6" s="167"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="168"/>
+      <c r="N6" s="168"/>
+      <c r="O6" s="165"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -3592,7 +3482,7 @@
         <v>2.63</v>
       </c>
       <c r="G7" s="24">
-        <v>104080.82107822559</v>
+        <v>104080.23140012554</v>
       </c>
       <c r="H7" s="29">
         <f>168983-G39</f>
@@ -3603,7 +3493,7 @@
       </c>
       <c r="J7" s="7">
         <f>H7-G7</f>
-        <v>0.26957097442937084</v>
+        <v>0.85924907447770238</v>
       </c>
       <c r="K7" s="40">
         <f>N$4*F7%</f>
@@ -3611,19 +3501,19 @@
       </c>
       <c r="L7" s="6">
         <f>N$3*F7%</f>
-        <v>104080.50097109997</v>
+        <v>121041.73688300001</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="23">
         <f>L7+K7-J7+M7</f>
-        <v>104080.23140012554</v>
+        <v>121040.87763392553</v>
       </c>
       <c r="O7" s="23">
         <f>N7*6% + N7</f>
-        <v>110325.04528413307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>128303.33029196106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -3641,7 +3531,7 @@
         <v>3.33</v>
       </c>
       <c r="G8" s="24">
-        <v>349863.1907638493</v>
+        <v>349862.72621394927</v>
       </c>
       <c r="H8" s="29">
         <f>131783</f>
@@ -3652,7 +3542,7 @@
       </c>
       <c r="J8" s="7">
         <f t="shared" ref="J8:J42" si="0">H8-G8</f>
-        <v>-218080.1907638493</v>
+        <v>-218079.72621394927</v>
       </c>
       <c r="K8" s="40">
         <f t="shared" ref="K8:K42" si="1">N$4*F8%</f>
@@ -3660,20 +3550,20 @@
       </c>
       <c r="L8" s="6">
         <f t="shared" ref="L8:L42" si="2">N$3*F8%</f>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M8" s="23"/>
       <c r="N8" s="23">
         <f>L8+K8-J8+M8</f>
-        <v>349862.72621394927</v>
+        <v>371337.89496694924</v>
       </c>
       <c r="O8" s="23">
         <f t="shared" ref="O8:O42" si="3">N8*6% + N8</f>
-        <v>370854.4897867862</v>
+        <v>393618.16866496619</v>
       </c>
       <c r="Q8" s="31"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -3689,18 +3579,18 @@
         <v>3.32</v>
       </c>
       <c r="G9" s="24">
-        <v>131386.79210039997</v>
+        <v>131387.14420079993</v>
       </c>
       <c r="H9" s="29">
-        <f>99904.44+31482</f>
-        <v>131386.44</v>
+        <f>99904.44+31482+1</f>
+        <v>131387.44</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>-0.35210039996309206</v>
+        <v>0.29579920007381588</v>
       </c>
       <c r="K9" s="40">
         <f t="shared" si="1"/>
@@ -3708,19 +3598,19 @@
       </c>
       <c r="L9" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23">
         <f t="shared" ref="N9:N42" si="4">L9+K9-J9+M9</f>
-        <v>131387.14420079993</v>
+        <v>152797.63821279994</v>
       </c>
       <c r="O9" s="23">
         <f t="shared" si="3"/>
-        <v>139270.37285284791</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>161965.49650556792</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -3736,7 +3626,7 @@
         <v>3.42</v>
       </c>
       <c r="G10" s="24">
-        <v>491417.68831600342</v>
+        <v>490761.9139134034</v>
       </c>
       <c r="H10" s="29">
         <f>136000</f>
@@ -3747,7 +3637,7 @@
       </c>
       <c r="J10" s="7">
         <f t="shared" si="0"/>
-        <v>-355417.68831600342</v>
+        <v>-354761.9139134034</v>
       </c>
       <c r="K10" s="40">
         <f t="shared" si="1"/>
@@ -3755,19 +3645,19 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="2"/>
-        <v>135344.22559739999</v>
+        <v>157400.281422</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23">
         <f t="shared" si="4"/>
-        <v>490761.9139134034</v>
+        <v>512162.19533540343</v>
       </c>
       <c r="O10" s="23">
         <f t="shared" si="3"/>
-        <v>520207.62874820759</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>542891.92705552769</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3802,19 +3692,19 @@
       </c>
       <c r="L11" s="6">
         <f t="shared" si="2"/>
-        <v>132178.27879979997</v>
+        <v>153718.403494</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23">
         <f t="shared" si="4"/>
-        <v>132178.27879979997</v>
+        <v>153718.403494</v>
       </c>
       <c r="O11" s="23">
         <f t="shared" si="3"/>
-        <v>140108.97552778796</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162941.50770364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3849,19 +3739,19 @@
       </c>
       <c r="L12" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="23">
         <f t="shared" si="4"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="O12" s="23">
         <f t="shared" si="3"/>
-        <v>139689.48757710596</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162453.65887817999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,19 +3786,19 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="23">
         <f t="shared" si="4"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="O13" s="23">
         <f t="shared" si="3"/>
-        <v>139269.99962642396</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>161965.81005272001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -3924,18 +3814,18 @@
         <v>3.33</v>
       </c>
       <c r="G14" s="24">
-        <v>131782.53545009997</v>
+        <v>131782.53090019993</v>
       </c>
       <c r="H14" s="29">
-        <f>100205.36+31577.18</f>
-        <v>131782.54</v>
+        <f>G14</f>
+        <v>131782.53090019993</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J14" s="7">
         <f t="shared" si="0"/>
-        <v>4.5499000407289714E-3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="40">
         <f t="shared" si="1"/>
@@ -3943,19 +3833,19 @@
       </c>
       <c r="L14" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M14" s="23"/>
       <c r="N14" s="23">
         <f t="shared" si="4"/>
-        <v>131782.53090019993</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="O14" s="23">
         <f t="shared" si="3"/>
-        <v>139689.48275421193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162453.65887817999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -3973,7 +3863,7 @@
         <v>3.24</v>
       </c>
       <c r="G15" s="24">
-        <v>204755.8907432048</v>
+        <v>204755.73604600481</v>
       </c>
       <c r="H15" s="29">
         <v>128221</v>
@@ -3983,7 +3873,7 @@
       </c>
       <c r="J15" s="7">
         <f t="shared" si="0"/>
-        <v>-76534.8907432048</v>
+        <v>-76534.736046004808</v>
       </c>
       <c r="K15" s="40">
         <f t="shared" si="1"/>
@@ -3991,22 +3881,22 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="23">
         <f t="shared" si="4"/>
-        <v>204755.73604600481</v>
+        <v>225650.79213000485</v>
       </c>
       <c r="O15" s="23">
         <f t="shared" si="3"/>
-        <v>217041.08020876511</v>
+        <v>239189.83965780513</v>
       </c>
       <c r="R15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -4024,7 +3914,7 @@
         <v>3.33</v>
       </c>
       <c r="G16" s="24">
-        <v>131782.53545009997</v>
+        <v>263565.07090019993</v>
       </c>
       <c r="H16" s="29"/>
       <c r="I16" s="13" t="s">
@@ -4032,7 +3922,7 @@
       </c>
       <c r="J16" s="7">
         <f t="shared" si="0"/>
-        <v>-131782.53545009997</v>
+        <v>-263565.07090019993</v>
       </c>
       <c r="K16" s="40">
         <f t="shared" si="1"/>
@@ -4040,19 +3930,19 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="23">
         <f>L16+K16-J16+M16</f>
-        <v>263565.07090019993</v>
+        <v>416823.23965319991</v>
       </c>
       <c r="O16" s="23">
         <f t="shared" si="3"/>
-        <v>279378.97515421192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>441832.63403239188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -4087,19 +3977,19 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="23">
         <f t="shared" si="4"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="O17" s="23">
         <f t="shared" si="3"/>
-        <v>139269.99962642396</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>161965.81005272001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
@@ -4115,18 +4005,18 @@
         <v>3.33</v>
       </c>
       <c r="G18" s="24">
-        <v>211782.53936730002</v>
+        <v>241782.07481739999</v>
       </c>
       <c r="H18" s="29">
-        <f>50000+51783</f>
-        <v>101783</v>
+        <f>30000</f>
+        <v>30000</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="0"/>
-        <v>-109999.53936730002</v>
+        <v>-211782.07481739999</v>
       </c>
       <c r="K18" s="40">
         <f t="shared" si="1"/>
@@ -4134,19 +4024,19 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="23">
         <f t="shared" si="4"/>
-        <v>241782.07481739999</v>
+        <v>365040.24357039999</v>
       </c>
       <c r="O18" s="23">
         <f t="shared" si="3"/>
-        <v>256288.99930644399</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>386942.65818462399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -4162,18 +4052,18 @@
         <v>3.24</v>
       </c>
       <c r="G19" s="24">
-        <v>128574.18954637241</v>
+        <v>128196.94419997238</v>
       </c>
       <c r="H19" s="29">
-        <f>130000+63500-H32</f>
-        <v>128598.09064920002</v>
+        <f>193000-H32</f>
+        <v>128098.09064920002</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="0"/>
-        <v>23.901102827614523</v>
+        <v>-98.853550772357266</v>
       </c>
       <c r="K19" s="40">
         <f t="shared" si="1"/>
@@ -4181,19 +4071,19 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="23">
         <f t="shared" si="4"/>
-        <v>128196.94419997238</v>
+        <v>149214.9096347724</v>
       </c>
       <c r="O19" s="23">
         <f t="shared" si="3"/>
-        <v>135888.76085197073</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>158167.80421285873</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -4211,7 +4101,7 @@
         <v>3.33</v>
       </c>
       <c r="G20" s="24">
-        <v>148017.32999999999</v>
+        <v>139799.86545009995</v>
       </c>
       <c r="H20" s="29">
         <v>140000</v>
@@ -4221,7 +4111,7 @@
       </c>
       <c r="J20" s="7">
         <f t="shared" si="0"/>
-        <v>-8017.3299999999872</v>
+        <v>200.13454990004539</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" si="1"/>
@@ -4229,19 +4119,19 @@
       </c>
       <c r="L20" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="23">
         <f t="shared" si="4"/>
-        <v>139799.86545009995</v>
+        <v>153058.03420309996</v>
       </c>
       <c r="O20" s="23">
         <f t="shared" si="3"/>
-        <v>148187.85737710595</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162241.51625528597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -4257,18 +4147,15 @@
         <v>3.32</v>
       </c>
       <c r="G21" s="24">
-        <v>655681.48441645608</v>
-      </c>
-      <c r="H21" s="29">
-        <f>458000-H35+200000</f>
-        <v>463294.27194760006</v>
-      </c>
+        <v>323774.00456925598</v>
+      </c>
+      <c r="H21" s="29"/>
       <c r="I21" s="13" t="s">
         <v>152</v>
       </c>
       <c r="J21" s="7">
         <f>H21-G21</f>
-        <v>-192387.21246885601</v>
+        <v>-323774.00456925598</v>
       </c>
       <c r="K21" s="40">
         <f t="shared" si="1"/>
@@ -4276,19 +4163,19 @@
       </c>
       <c r="L21" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="23">
         <f t="shared" si="4"/>
-        <v>323774.00456925598</v>
+        <v>476571.93858125596</v>
       </c>
       <c r="O21" s="23">
         <f t="shared" si="3"/>
-        <v>343200.44484341133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>505166.25489613134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -4304,7 +4191,7 @@
         <v>3.33</v>
       </c>
       <c r="G22" s="13">
-        <v>1732104.5207638489</v>
+        <v>1863887.0562139489</v>
       </c>
       <c r="H22" s="29"/>
       <c r="I22" s="13" t="s">
@@ -4312,7 +4199,7 @@
       </c>
       <c r="J22" s="43">
         <f t="shared" si="0"/>
-        <v>-1732104.5207638489</v>
+        <v>-1863887.0562139489</v>
       </c>
       <c r="K22" s="40">
         <f t="shared" si="1"/>
@@ -4320,20 +4207,20 @@
       </c>
       <c r="L22" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="23">
         <f t="shared" si="4"/>
-        <v>1863887.0562139489</v>
+        <v>2017145.2249669489</v>
       </c>
       <c r="O22" s="23">
         <f t="shared" si="3"/>
-        <v>1975720.2795867857</v>
+        <v>2138173.9384649657</v>
       </c>
       <c r="R22" s="30"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -4351,18 +4238,18 @@
         <v>3.24</v>
       </c>
       <c r="G23" s="24">
-        <v>384661.86239296006</v>
+        <v>128220.70769576005</v>
       </c>
       <c r="H23" s="29">
-        <f>128700+128321+127641</f>
-        <v>384662</v>
+        <f>G23</f>
+        <v>128220.70769576005</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>140</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
-        <v>0.13760703994194046</v>
+        <v>0</v>
       </c>
       <c r="K23" s="40">
         <f t="shared" si="1"/>
@@ -4370,19 +4257,19 @@
       </c>
       <c r="L23" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="23">
         <f t="shared" si="4"/>
-        <v>128220.70769576005</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="O23" s="23">
         <f t="shared" si="3"/>
-        <v>135913.95015750566</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>158063.01944904003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -4398,17 +4285,17 @@
         <v>3.24</v>
       </c>
       <c r="G24" s="24">
-        <v>120054.91938440005</v>
+        <v>121017.76468720005</v>
       </c>
       <c r="H24" s="29">
-        <v>127258</v>
+        <v>129000</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
-        <v>7203.0806155999453</v>
+        <v>7982.2353127999522</v>
       </c>
       <c r="K24" s="40">
         <f t="shared" si="1"/>
@@ -4416,19 +4303,19 @@
       </c>
       <c r="L24" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="23">
         <f t="shared" si="4"/>
-        <v>121017.76468720005</v>
+        <v>141133.82077120009</v>
       </c>
       <c r="O24" s="23">
         <f t="shared" si="3"/>
-        <v>128278.83056843205</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>149601.85001747208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -4446,18 +4333,18 @@
         <v>3.32</v>
       </c>
       <c r="G25" s="24">
-        <v>119609.98920999994</v>
+        <v>131388.69066119989</v>
       </c>
       <c r="H25" s="29">
-        <f>184510-H33</f>
-        <v>119608.09064920002</v>
+        <f>196290-H33</f>
+        <v>131388.09064920002</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
-        <v>-1.898560799920233</v>
+        <v>-0.60001199986436404</v>
       </c>
       <c r="K25" s="40">
         <f t="shared" si="1"/>
@@ -4465,19 +4352,19 @@
       </c>
       <c r="L25" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="23">
         <f t="shared" si="4"/>
-        <v>131388.69066119989</v>
+        <v>152798.53402399988</v>
       </c>
       <c r="O25" s="23">
         <f t="shared" si="3"/>
-        <v>139272.01210087189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>161966.44606543987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -4514,19 +4401,19 @@
       </c>
       <c r="L26" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="23">
         <f t="shared" si="4"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="O26" s="23">
         <f t="shared" si="3"/>
-        <v>139689.48757710596</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162453.65887817999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -4544,18 +4431,18 @@
         <v>3.24</v>
       </c>
       <c r="G27" s="24">
-        <v>256441.29572003422</v>
+        <v>128221.14102283421</v>
       </c>
       <c r="H27" s="29">
-        <f>115500+128221+12720</f>
-        <v>256441</v>
+        <f>G27</f>
+        <v>128221.14102283421</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>152</v>
       </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
-        <v>-0.29572003422072157</v>
+        <v>0</v>
       </c>
       <c r="K27" s="40">
         <f t="shared" si="1"/>
@@ -4563,19 +4450,19 @@
       </c>
       <c r="L27" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="23">
         <f t="shared" si="4"/>
-        <v>128221.14102283421</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="O27" s="23">
         <f t="shared" si="3"/>
-        <v>135914.40948420425</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>158063.01944904003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -4610,19 +4497,19 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="23">
         <f t="shared" si="4"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="O28" s="23">
         <f t="shared" si="3"/>
-        <v>139689.48757710596</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162453.65887817999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -4638,18 +4525,15 @@
         <v>3.32</v>
       </c>
       <c r="G29" s="24">
-        <v>131387.19936919998</v>
-      </c>
-      <c r="H29" s="29">
-        <f>G29</f>
-        <v>131387.19936919998</v>
-      </c>
+        <v>131386.79210039997</v>
+      </c>
+      <c r="H29" s="29"/>
       <c r="I29" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J29" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-131386.79210039997</v>
       </c>
       <c r="K29" s="40">
         <f t="shared" si="1"/>
@@ -4657,19 +4541,19 @@
       </c>
       <c r="L29" s="6">
         <f t="shared" si="2"/>
-        <v>131386.79210039997</v>
+        <v>152797.93401200001</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23">
         <f t="shared" si="4"/>
-        <v>131386.79210039997</v>
+        <v>284184.72611239995</v>
       </c>
       <c r="O29" s="23">
         <f t="shared" si="3"/>
-        <v>139269.99962642396</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>301235.80967914395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -4706,19 +4590,19 @@
       </c>
       <c r="L30" s="6">
         <f t="shared" si="2"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23">
         <f t="shared" si="4"/>
-        <v>131782.53545009997</v>
+        <v>153258.16875300001</v>
       </c>
       <c r="O30" s="23">
         <f t="shared" si="3"/>
-        <v>139689.48757710596</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>162453.65887817999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -4726,15 +4610,15 @@
       <c r="C31" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="149" t="s">
-        <v>194</v>
+      <c r="D31" s="144" t="s">
+        <v>186</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="1">
         <v>3.24</v>
       </c>
       <c r="G31" s="24">
-        <v>762500.11076129321</v>
+        <v>762499.95606409316</v>
       </c>
       <c r="H31" s="29">
         <v>128221</v>
@@ -4744,7 +4628,7 @@
       </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
-        <v>-634279.11076129321</v>
+        <v>-634278.95606409316</v>
       </c>
       <c r="K31" s="40">
         <f t="shared" si="1"/>
@@ -4752,19 +4636,19 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="2"/>
-        <v>128220.84530279999</v>
+        <v>149116.05608400004</v>
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="23">
         <f>L31+K31-J31+M31</f>
-        <v>762499.95606409316</v>
+        <v>783395.0121480932</v>
       </c>
       <c r="O31" s="23">
         <f t="shared" si="3"/>
-        <v>808249.95342793874</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>830398.7128769788</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -4799,19 +4683,19 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O32" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -4846,19 +4730,19 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O33" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -4874,17 +4758,17 @@
         <v>1.64</v>
       </c>
       <c r="G34" s="24">
-        <v>127283.42996256729</v>
+        <v>62185.339313367265</v>
       </c>
       <c r="H34" s="29">
-        <v>130000</v>
+        <v>63000</v>
       </c>
       <c r="I34" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
-        <v>2716.5700374327134</v>
+        <v>814.66068663273472</v>
       </c>
       <c r="K34" s="40">
         <f t="shared" si="1"/>
@@ -4892,19 +4776,19 @@
       </c>
       <c r="L34" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="23">
         <f t="shared" si="4"/>
-        <v>62185.339313367265</v>
+        <v>74663.836837367257</v>
       </c>
       <c r="O34" s="23">
         <f t="shared" si="3"/>
-        <v>65916.459672169294</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+        <v>79143.667047609284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -4920,18 +4804,15 @@
         <v>1.64</v>
       </c>
       <c r="G35" s="24">
-        <v>194705.72805239997</v>
-      </c>
-      <c r="H35" s="29">
-        <f>G35</f>
-        <v>194705.72805239997</v>
-      </c>
+        <v>64901.909350799979</v>
+      </c>
+      <c r="H35" s="29"/>
       <c r="I35" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J35" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-64901.909350799979</v>
       </c>
       <c r="K35" s="40">
         <f t="shared" si="1"/>
@@ -4939,19 +4820,22 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>140380.40687479998</v>
       </c>
       <c r="O35" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+        <v>148803.23128728798</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -4986,19 +4870,19 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O36" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -5033,19 +4917,19 @@
       </c>
       <c r="L37" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O37" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -5061,7 +4945,7 @@
         <v>1.64</v>
       </c>
       <c r="G38" s="24">
-        <v>853048.47815396765</v>
+        <v>917950.38750476763</v>
       </c>
       <c r="H38" s="29"/>
       <c r="I38" s="13" t="s">
@@ -5069,7 +4953,7 @@
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
-        <v>-853048.47815396765</v>
+        <v>-917950.38750476763</v>
       </c>
       <c r="K38" s="40">
         <f t="shared" si="1"/>
@@ -5077,19 +4961,19 @@
       </c>
       <c r="L38" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="23">
         <f t="shared" si="4"/>
-        <v>917950.38750476763</v>
+        <v>993428.88502876763</v>
       </c>
       <c r="O38" s="23">
         <f t="shared" si="3"/>
-        <v>973027.41075505363</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1053034.6181304937</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -5124,19 +5008,19 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O39" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>36</v>
       </c>
@@ -5173,19 +5057,19 @@
       </c>
       <c r="L40" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="23">
         <f t="shared" si="4"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="O40" s="23">
         <f t="shared" si="3"/>
-        <v>68796.02391184798</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>80007.20737543999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -5201,17 +5085,17 @@
         <v>1.64</v>
       </c>
       <c r="G41" s="24">
-        <v>57332.05713079992</v>
+        <v>61461.966481599899</v>
       </c>
       <c r="H41" s="29">
-        <v>60772</v>
+        <v>65150</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J41" s="7">
         <f t="shared" si="0"/>
-        <v>3439.9428692000802</v>
+        <v>3688.0335184001015</v>
       </c>
       <c r="K41" s="40">
         <f t="shared" si="1"/>
@@ -5219,19 +5103,19 @@
       </c>
       <c r="L41" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="23">
         <f t="shared" si="4"/>
-        <v>61461.966481599899</v>
+        <v>71790.46400559989</v>
       </c>
       <c r="O41" s="23">
         <f t="shared" si="3"/>
-        <v>65149.684470495893</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76097.891845935883</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>36</v>
       </c>
@@ -5247,15 +5131,18 @@
         <v>1.64</v>
       </c>
       <c r="G42" s="24">
-        <v>129803.81870159997</v>
-      </c>
-      <c r="H42" s="29"/>
+        <v>194705.72805239994</v>
+      </c>
+      <c r="H42" s="29">
+        <f>131386</f>
+        <v>131386</v>
+      </c>
       <c r="I42" s="13" t="s">
         <v>123</v>
       </c>
       <c r="J42" s="7">
         <f t="shared" si="0"/>
-        <v>-129803.81870159997</v>
+        <v>-63319.728052399936</v>
       </c>
       <c r="K42" s="40">
         <f t="shared" si="1"/>
@@ -5263,19 +5150,19 @@
       </c>
       <c r="L42" s="6">
         <f t="shared" si="2"/>
-        <v>64901.909350799979</v>
+        <v>75478.497523999991</v>
       </c>
       <c r="M42" s="23"/>
       <c r="N42" s="23">
         <f t="shared" si="4"/>
-        <v>194705.72805239994</v>
+        <v>138798.22557639994</v>
       </c>
       <c r="O42" s="23">
         <f t="shared" si="3"/>
-        <v>206388.07173554393</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147126.11911098394</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -5287,16 +5174,16 @@
       </c>
       <c r="G43" s="9">
         <f>SUM(G7:G42)</f>
-        <v>8869551.8677408844</v>
+        <v>8389069.1426655836</v>
       </c>
       <c r="H43" s="9">
         <f>SUM(H7:H42)</f>
-        <v>4441477.9122226005</v>
+        <v>3277433.5524721928</v>
       </c>
       <c r="I43" s="9"/>
-      <c r="J43" s="141">
+      <c r="J43" s="139">
         <f t="shared" ref="J43:O43" si="5">SUM(J7:J42)</f>
-        <v>-4428073.955518282</v>
+        <v>-5111635.5901933871</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="5"/>
@@ -5304,7 +5191,7 @@
       </c>
       <c r="L43" s="9">
         <f t="shared" si="5"/>
-        <v>3960995.1871472988</v>
+        <v>4606489.5226689978</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="5"/>
@@ -5312,120 +5199,120 @@
       </c>
       <c r="N43" s="10">
         <f t="shared" si="5"/>
-        <v>8389069.1426655836</v>
+        <v>9718125.1128623914</v>
       </c>
       <c r="O43" s="9">
         <f t="shared" si="5"/>
-        <v>8892413.2912255153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>10301212.619634137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" t="s">
         <v>121</v>
       </c>
       <c r="I44">
         <f>SUMIF(I7:I42,"b",H7:H42)</f>
-        <v>3730327.6487200996</v>
+        <v>2822724.5812739334</v>
       </c>
       <c r="L44" s="11"/>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" t="s">
         <v>122</v>
       </c>
       <c r="I45">
         <f>SUMIF(I7:I42,"e",H7:H42)</f>
-        <v>711150.2635024999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>454708.97119825997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
         <v>16</v>
       </c>
       <c r="H46" s="36">
         <f>I44+I45</f>
-        <v>4441477.9122225996</v>
-      </c>
-    </row>
-    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D49" s="168" t="s">
+        <v>3277433.5524721933</v>
+      </c>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D49" s="159" t="s">
         <v>182</v>
       </c>
-      <c r="E49" s="168"/>
-      <c r="F49" s="168"/>
-      <c r="G49" s="168"/>
-      <c r="H49" s="168"/>
-      <c r="I49" s="168"/>
-      <c r="J49" s="168"/>
-      <c r="K49" s="168"/>
-      <c r="L49" s="168"/>
-      <c r="M49" s="168"/>
-      <c r="N49" s="168"/>
-    </row>
-    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D50" s="168"/>
-      <c r="E50" s="168"/>
-      <c r="F50" s="168"/>
-      <c r="G50" s="168"/>
-      <c r="H50" s="168"/>
-      <c r="I50" s="168"/>
-      <c r="J50" s="168"/>
-      <c r="K50" s="168"/>
-      <c r="L50" s="168"/>
-      <c r="M50" s="168"/>
-      <c r="N50" s="168"/>
-    </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D51" s="168"/>
-      <c r="E51" s="168"/>
-      <c r="F51" s="168"/>
-      <c r="G51" s="168"/>
-      <c r="H51" s="168"/>
-      <c r="I51" s="168"/>
-      <c r="J51" s="168"/>
-      <c r="K51" s="168"/>
-      <c r="L51" s="168"/>
-      <c r="M51" s="168"/>
-      <c r="N51" s="168"/>
-    </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D52" s="168"/>
-      <c r="E52" s="168"/>
-      <c r="F52" s="168"/>
-      <c r="G52" s="168"/>
-      <c r="H52" s="168"/>
-      <c r="I52" s="168"/>
-      <c r="J52" s="168"/>
-      <c r="K52" s="168"/>
-      <c r="L52" s="168"/>
-      <c r="M52" s="168"/>
-      <c r="N52" s="168"/>
-    </row>
-    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D53" s="168"/>
-      <c r="E53" s="168"/>
-      <c r="F53" s="168"/>
-      <c r="G53" s="168"/>
-      <c r="H53" s="168"/>
-      <c r="I53" s="168"/>
-      <c r="J53" s="168"/>
-      <c r="K53" s="168"/>
-      <c r="L53" s="168"/>
-      <c r="M53" s="168"/>
-      <c r="N53" s="168"/>
-    </row>
-    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D54" s="168"/>
-      <c r="E54" s="168"/>
-      <c r="F54" s="168"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="168"/>
-      <c r="I54" s="168"/>
-      <c r="J54" s="168"/>
-      <c r="K54" s="168"/>
-      <c r="L54" s="168"/>
-      <c r="M54" s="168"/>
-      <c r="N54" s="168"/>
+      <c r="E49" s="159"/>
+      <c r="F49" s="159"/>
+      <c r="G49" s="159"/>
+      <c r="H49" s="159"/>
+      <c r="I49" s="159"/>
+      <c r="J49" s="159"/>
+      <c r="K49" s="159"/>
+      <c r="L49" s="159"/>
+      <c r="M49" s="159"/>
+      <c r="N49" s="159"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D50" s="159"/>
+      <c r="E50" s="159"/>
+      <c r="F50" s="159"/>
+      <c r="G50" s="159"/>
+      <c r="H50" s="159"/>
+      <c r="I50" s="159"/>
+      <c r="J50" s="159"/>
+      <c r="K50" s="159"/>
+      <c r="L50" s="159"/>
+      <c r="M50" s="159"/>
+      <c r="N50" s="159"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D51" s="159"/>
+      <c r="E51" s="159"/>
+      <c r="F51" s="159"/>
+      <c r="G51" s="159"/>
+      <c r="H51" s="159"/>
+      <c r="I51" s="159"/>
+      <c r="J51" s="159"/>
+      <c r="K51" s="159"/>
+      <c r="L51" s="159"/>
+      <c r="M51" s="159"/>
+      <c r="N51" s="159"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D52" s="159"/>
+      <c r="E52" s="159"/>
+      <c r="F52" s="159"/>
+      <c r="G52" s="159"/>
+      <c r="H52" s="159"/>
+      <c r="I52" s="159"/>
+      <c r="J52" s="159"/>
+      <c r="K52" s="159"/>
+      <c r="L52" s="159"/>
+      <c r="M52" s="159"/>
+      <c r="N52" s="159"/>
+    </row>
+    <row r="53" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D53" s="159"/>
+      <c r="E53" s="159"/>
+      <c r="F53" s="159"/>
+      <c r="G53" s="159"/>
+      <c r="H53" s="159"/>
+      <c r="I53" s="159"/>
+      <c r="J53" s="159"/>
+      <c r="K53" s="159"/>
+      <c r="L53" s="159"/>
+      <c r="M53" s="159"/>
+      <c r="N53" s="159"/>
+    </row>
+    <row r="54" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D54" s="159"/>
+      <c r="E54" s="159"/>
+      <c r="F54" s="159"/>
+      <c r="G54" s="159"/>
+      <c r="H54" s="159"/>
+      <c r="I54" s="159"/>
+      <c r="J54" s="159"/>
+      <c r="K54" s="159"/>
+      <c r="L54" s="159"/>
+      <c r="M54" s="159"/>
+      <c r="N54" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -5455,36 +5342,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E6:O38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="190" t="s">
+    <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="181" t="s">
         <v>165</v>
       </c>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="191"/>
-      <c r="I7" s="191"/>
-      <c r="J7" s="191"/>
-      <c r="K7" s="189"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="180"/>
       <c r="L7" s="44"/>
       <c r="M7" s="45"/>
     </row>
-    <row r="8" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="192" t="s">
+    <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="183" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="191"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="189"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="180"/>
       <c r="L8" s="46"/>
       <c r="M8" s="47"/>
     </row>
-    <row r="9" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E9" s="44"/>
       <c r="F9" s="48"/>
       <c r="G9" s="48"/>
@@ -5497,7 +5384,7 @@
       <c r="L9" s="46"/>
       <c r="M9" s="47"/>
     </row>
-    <row r="10" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E10" s="46" t="s">
         <v>168</v>
       </c>
@@ -5512,7 +5399,7 @@
       <c r="L10" s="46"/>
       <c r="M10" s="47"/>
     </row>
-    <row r="11" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E11" s="50"/>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
@@ -5523,20 +5410,20 @@
       <c r="L11" s="46"/>
       <c r="M11" s="47"/>
     </row>
-    <row r="12" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="193" t="s">
+    <row r="12" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="184" t="s">
         <v>170</v>
       </c>
-      <c r="F12" s="194"/>
-      <c r="G12" s="194"/>
-      <c r="H12" s="194"/>
-      <c r="I12" s="194"/>
-      <c r="J12" s="194"/>
-      <c r="K12" s="195"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="186"/>
       <c r="L12" s="46"/>
       <c r="M12" s="47"/>
     </row>
-    <row r="13" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E13" s="46"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
@@ -5547,7 +5434,7 @@
       <c r="L13" s="46"/>
       <c r="M13" s="47"/>
     </row>
-    <row r="14" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E14" s="46" t="s">
         <v>171</v>
       </c>
@@ -5564,12 +5451,12 @@
         <v>45600</v>
       </c>
       <c r="K14" s="47"/>
-      <c r="L14" s="183" t="s">
+      <c r="L14" s="174" t="s">
         <v>173</v>
       </c>
-      <c r="M14" s="184"/>
-    </row>
-    <row r="15" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="175"/>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E15" s="46" t="s">
         <v>174</v>
       </c>
@@ -5585,7 +5472,7 @@
       <c r="L15" s="46"/>
       <c r="M15" s="47"/>
     </row>
-    <row r="16" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E16" s="46"/>
       <c r="F16" s="49"/>
       <c r="G16" s="49"/>
@@ -5593,10 +5480,10 @@
       <c r="I16" s="49"/>
       <c r="J16" s="49"/>
       <c r="K16" s="47"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="184"/>
-    </row>
-    <row r="17" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="L16" s="176"/>
+      <c r="M16" s="175"/>
+    </row>
+    <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" s="46"/>
       <c r="F17" s="49"/>
       <c r="G17" s="49"/>
@@ -5607,7 +5494,7 @@
       <c r="L17" s="46"/>
       <c r="M17" s="47"/>
     </row>
-    <row r="18" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E18" s="46"/>
       <c r="F18" s="49"/>
       <c r="G18" s="49"/>
@@ -5618,7 +5505,7 @@
       <c r="L18" s="46"/>
       <c r="M18" s="47"/>
     </row>
-    <row r="19" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E19" s="46"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
@@ -5629,50 +5516,50 @@
       <c r="L19" s="55"/>
       <c r="M19" s="56"/>
     </row>
-    <row r="20" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="186" t="s">
+    <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="177" t="s">
         <v>175</v>
       </c>
-      <c r="F20" s="187"/>
-      <c r="G20" s="187"/>
-      <c r="H20" s="187"/>
-      <c r="I20" s="187"/>
-      <c r="J20" s="188">
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="178"/>
+      <c r="J20" s="179">
         <f>PRORRATEO!H12</f>
         <v>131782.53545009997</v>
       </c>
-      <c r="K20" s="189"/>
+      <c r="K20" s="180"/>
       <c r="L20" s="57"/>
       <c r="M20" s="58"/>
     </row>
-    <row r="24" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="190" t="s">
+    <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="181" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="191"/>
-      <c r="I25" s="191"/>
-      <c r="J25" s="191"/>
-      <c r="K25" s="191"/>
-      <c r="L25" s="191"/>
-      <c r="M25" s="189"/>
+      <c r="H25" s="182"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="180"/>
       <c r="N25" s="44"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G26" s="192" t="s">
+    <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="183" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="191"/>
-      <c r="I26" s="191"/>
-      <c r="J26" s="191"/>
-      <c r="K26" s="191"/>
-      <c r="L26" s="191"/>
-      <c r="M26" s="189"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="180"/>
       <c r="N26" s="46"/>
       <c r="O26" s="47"/>
     </row>
-    <row r="27" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G27" s="44"/>
       <c r="H27" s="48"/>
       <c r="I27" s="48"/>
@@ -5685,7 +5572,7 @@
       <c r="N27" s="46"/>
       <c r="O27" s="47"/>
     </row>
-    <row r="28" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G28" s="46" t="s">
         <v>168</v>
       </c>
@@ -5700,7 +5587,7 @@
       <c r="N28" s="46"/>
       <c r="O28" s="47"/>
     </row>
-    <row r="29" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G29" s="50"/>
       <c r="H29" s="51"/>
       <c r="I29" s="51"/>
@@ -5711,20 +5598,20 @@
       <c r="N29" s="46"/>
       <c r="O29" s="47"/>
     </row>
-    <row r="30" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G30" s="193" t="s">
+    <row r="30" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G30" s="184" t="s">
         <v>170</v>
       </c>
-      <c r="H30" s="194"/>
-      <c r="I30" s="194"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="194"/>
-      <c r="L30" s="194"/>
-      <c r="M30" s="195"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="186"/>
       <c r="N30" s="46"/>
       <c r="O30" s="47"/>
     </row>
-    <row r="31" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G31" s="46"/>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
@@ -5735,7 +5622,7 @@
       <c r="N31" s="46"/>
       <c r="O31" s="47"/>
     </row>
-    <row r="32" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G32" s="46" t="s">
         <v>171</v>
       </c>
@@ -5749,12 +5636,12 @@
         <v>45600</v>
       </c>
       <c r="M32" s="47"/>
-      <c r="N32" s="183" t="s">
+      <c r="N32" s="174" t="s">
         <v>173</v>
       </c>
-      <c r="O32" s="184"/>
-    </row>
-    <row r="33" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="O32" s="175"/>
+    </row>
+    <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="46" t="s">
         <v>174</v>
       </c>
@@ -5770,7 +5657,7 @@
       <c r="N33" s="46"/>
       <c r="O33" s="47"/>
     </row>
-    <row r="34" spans="7:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G34" s="46"/>
       <c r="H34" s="49"/>
       <c r="I34" s="49"/>
@@ -5778,10 +5665,10 @@
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
       <c r="M34" s="47"/>
-      <c r="N34" s="185"/>
-      <c r="O34" s="184"/>
-    </row>
-    <row r="35" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="N34" s="176"/>
+      <c r="O34" s="175"/>
+    </row>
+    <row r="35" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G35" s="46"/>
       <c r="H35" s="49"/>
       <c r="I35" s="49"/>
@@ -5792,7 +5679,7 @@
       <c r="N35" s="46"/>
       <c r="O35" s="47"/>
     </row>
-    <row r="36" spans="7:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G36" s="46"/>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
@@ -5803,7 +5690,7 @@
       <c r="N36" s="46"/>
       <c r="O36" s="47"/>
     </row>
-    <row r="37" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G37" s="46"/>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
@@ -5814,19 +5701,19 @@
       <c r="N37" s="55"/>
       <c r="O37" s="56"/>
     </row>
-    <row r="38" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="186" t="s">
+    <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="177" t="s">
         <v>175</v>
       </c>
-      <c r="H38" s="187"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="187"/>
-      <c r="L38" s="188">
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="179">
         <f>PRORRATEO!J30</f>
         <v>0</v>
       </c>
-      <c r="M38" s="189"/>
+      <c r="M38" s="180"/>
       <c r="N38" s="57"/>
       <c r="O38" s="58"/>
     </row>

--- a/ALCORTA 146/Mayo/MAYO.xlsx
+++ b/ALCORTA 146/Mayo/MAYO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD05756-2925-4BB7-AE24-DE94CB76C36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B373F8-0FE2-472F-80CB-FA9683696EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="204">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA - ABONO VACACIONES ENCARGADO - ADEUDADAS</t>
+  </si>
+  <si>
+    <t>MARIA GARCIA CRISTINA</t>
   </si>
 </sst>
 </file>
@@ -1624,6 +1627,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1666,6 +1672,27 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1674,12 +1701,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1695,21 +1716,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1734,9 +1740,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2234,34 +2237,34 @@
       <c r="E14" s="71"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="147" t="s">
         <v>188</v>
       </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
+      <c r="B15" s="147"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="146"/>
-      <c r="B16" s="146"/>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
+      <c r="A16" s="147"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="146"/>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="146"/>
+      <c r="A17" s="147"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="146"/>
-      <c r="D18" s="146"/>
-      <c r="E18" s="146"/>
+      <c r="A18" s="147"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="71"/>
@@ -2285,39 +2288,39 @@
       <c r="E21" s="71"/>
     </row>
     <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="147"/>
-      <c r="B22" s="148"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="148"/>
-      <c r="E22" s="148"/>
+      <c r="A22" s="148"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="148"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="149"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="148"/>
-      <c r="B24" s="148"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
+      <c r="A24" s="149"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="148"/>
-      <c r="B25" s="148"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
+      <c r="A25" s="149"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="148"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
+      <c r="A26" s="149"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="71"/>
@@ -2735,7 +2738,7 @@
       </c>
       <c r="B65" s="78"/>
       <c r="C65" s="78"/>
-      <c r="D65" s="187">
+      <c r="D65" s="145">
         <v>96090.5</v>
       </c>
       <c r="E65" s="143"/>
@@ -2938,40 +2941,40 @@
       <c r="F85" s="31"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="157" t="s">
+      <c r="A86" s="158" t="s">
         <v>158</v>
       </c>
-      <c r="B86" s="158"/>
+      <c r="B86" s="159"/>
       <c r="C86" s="110"/>
       <c r="D86" s="71"/>
       <c r="E86" s="71"/>
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="149"/>
-      <c r="B87" s="150"/>
+      <c r="A87" s="150"/>
+      <c r="B87" s="151"/>
       <c r="C87" s="17"/>
       <c r="D87" s="71"/>
       <c r="E87" s="71"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="151"/>
-      <c r="B88" s="152"/>
+      <c r="A88" s="152"/>
+      <c r="B88" s="153"/>
       <c r="C88" s="17"/>
       <c r="D88" s="71"/>
       <c r="E88" s="71"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="153"/>
-      <c r="B89" s="154"/>
+      <c r="A89" s="154"/>
+      <c r="B89" s="155"/>
       <c r="C89" s="111"/>
       <c r="D89" s="71"/>
       <c r="E89" s="112"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="155" t="s">
+      <c r="A90" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="156"/>
+      <c r="B90" s="157"/>
       <c r="C90" s="113">
         <f>SUM(C87:C89)</f>
         <v>0</v>
@@ -3070,16 +3073,16 @@
       <c r="E99" s="71"/>
     </row>
     <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="148"/>
-      <c r="B100" s="148"/>
-      <c r="C100" s="148"/>
+      <c r="A100" s="149"/>
+      <c r="B100" s="149"/>
+      <c r="C100" s="149"/>
       <c r="D100" s="71"/>
       <c r="E100" s="71"/>
     </row>
     <row r="101" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="148"/>
-      <c r="B101" s="148"/>
-      <c r="C101" s="148"/>
+      <c r="A101" s="149"/>
+      <c r="B101" s="149"/>
+      <c r="C101" s="149"/>
       <c r="D101" s="71"/>
       <c r="E101" s="71"/>
     </row>
@@ -3252,16 +3255,16 @@
       <c r="E119" s="71"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="145" t="s">
+      <c r="A121" s="146" t="s">
         <v>164</v>
       </c>
-      <c r="B121" s="145"/>
-      <c r="C121" s="145"/>
+      <c r="B121" s="146"/>
+      <c r="C121" s="146"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="145"/>
-      <c r="B122" s="145"/>
-      <c r="C122" s="145"/>
+      <c r="A122" s="146"/>
+      <c r="B122" s="146"/>
+      <c r="C122" s="146"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
@@ -3378,11 +3381,11 @@
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="161">
+      <c r="N3" s="169">
         <f>O2</f>
         <v>4602347.41</v>
       </c>
-      <c r="O3" s="161"/>
+      <c r="O3" s="169"/>
       <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3401,70 +3404,70 @@
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="160"/>
-      <c r="O4" s="160"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="168"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="171" t="s">
+      <c r="C5" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="171" t="s">
+      <c r="D5" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="171" t="s">
+      <c r="E5" s="164" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="162" t="s">
+      <c r="F5" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="162" t="s">
+      <c r="G5" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="162" t="s">
+      <c r="H5" s="160" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="166" t="s">
+      <c r="J5" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="K5" s="164" t="s">
+      <c r="K5" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="164" t="s">
+      <c r="L5" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="164" t="s">
+      <c r="M5" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="164" t="s">
+      <c r="N5" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="164" t="s">
+      <c r="O5" s="170" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="163"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="163"/>
-      <c r="H6" s="163"/>
+      <c r="A6" s="161"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="167"/>
-      <c r="K6" s="165"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="168"/>
-      <c r="O6" s="165"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="171"/>
+      <c r="L6" s="174"/>
+      <c r="M6" s="174"/>
+      <c r="N6" s="174"/>
+      <c r="O6" s="171"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4551,6 +4554,9 @@
       <c r="O29" s="23">
         <f t="shared" si="3"/>
         <v>301235.80967914395</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5235,93 +5241,87 @@
       </c>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D49" s="159" t="s">
+      <c r="D49" s="167" t="s">
         <v>182</v>
       </c>
-      <c r="E49" s="159"/>
-      <c r="F49" s="159"/>
-      <c r="G49" s="159"/>
-      <c r="H49" s="159"/>
-      <c r="I49" s="159"/>
-      <c r="J49" s="159"/>
-      <c r="K49" s="159"/>
-      <c r="L49" s="159"/>
-      <c r="M49" s="159"/>
-      <c r="N49" s="159"/>
+      <c r="E49" s="167"/>
+      <c r="F49" s="167"/>
+      <c r="G49" s="167"/>
+      <c r="H49" s="167"/>
+      <c r="I49" s="167"/>
+      <c r="J49" s="167"/>
+      <c r="K49" s="167"/>
+      <c r="L49" s="167"/>
+      <c r="M49" s="167"/>
+      <c r="N49" s="167"/>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D50" s="159"/>
-      <c r="E50" s="159"/>
-      <c r="F50" s="159"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="159"/>
-      <c r="I50" s="159"/>
-      <c r="J50" s="159"/>
-      <c r="K50" s="159"/>
-      <c r="L50" s="159"/>
-      <c r="M50" s="159"/>
-      <c r="N50" s="159"/>
+      <c r="D50" s="167"/>
+      <c r="E50" s="167"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="167"/>
+      <c r="H50" s="167"/>
+      <c r="I50" s="167"/>
+      <c r="J50" s="167"/>
+      <c r="K50" s="167"/>
+      <c r="L50" s="167"/>
+      <c r="M50" s="167"/>
+      <c r="N50" s="167"/>
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D51" s="159"/>
-      <c r="E51" s="159"/>
-      <c r="F51" s="159"/>
-      <c r="G51" s="159"/>
-      <c r="H51" s="159"/>
-      <c r="I51" s="159"/>
-      <c r="J51" s="159"/>
-      <c r="K51" s="159"/>
-      <c r="L51" s="159"/>
-      <c r="M51" s="159"/>
-      <c r="N51" s="159"/>
+      <c r="D51" s="167"/>
+      <c r="E51" s="167"/>
+      <c r="F51" s="167"/>
+      <c r="G51" s="167"/>
+      <c r="H51" s="167"/>
+      <c r="I51" s="167"/>
+      <c r="J51" s="167"/>
+      <c r="K51" s="167"/>
+      <c r="L51" s="167"/>
+      <c r="M51" s="167"/>
+      <c r="N51" s="167"/>
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D52" s="159"/>
-      <c r="E52" s="159"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="159"/>
-      <c r="H52" s="159"/>
-      <c r="I52" s="159"/>
-      <c r="J52" s="159"/>
-      <c r="K52" s="159"/>
-      <c r="L52" s="159"/>
-      <c r="M52" s="159"/>
-      <c r="N52" s="159"/>
+      <c r="D52" s="167"/>
+      <c r="E52" s="167"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="167"/>
+      <c r="H52" s="167"/>
+      <c r="I52" s="167"/>
+      <c r="J52" s="167"/>
+      <c r="K52" s="167"/>
+      <c r="L52" s="167"/>
+      <c r="M52" s="167"/>
+      <c r="N52" s="167"/>
     </row>
     <row r="53" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D53" s="159"/>
-      <c r="E53" s="159"/>
-      <c r="F53" s="159"/>
-      <c r="G53" s="159"/>
-      <c r="H53" s="159"/>
-      <c r="I53" s="159"/>
-      <c r="J53" s="159"/>
-      <c r="K53" s="159"/>
-      <c r="L53" s="159"/>
-      <c r="M53" s="159"/>
-      <c r="N53" s="159"/>
+      <c r="D53" s="167"/>
+      <c r="E53" s="167"/>
+      <c r="F53" s="167"/>
+      <c r="G53" s="167"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
+      <c r="J53" s="167"/>
+      <c r="K53" s="167"/>
+      <c r="L53" s="167"/>
+      <c r="M53" s="167"/>
+      <c r="N53" s="167"/>
     </row>
     <row r="54" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D54" s="159"/>
-      <c r="E54" s="159"/>
-      <c r="F54" s="159"/>
-      <c r="G54" s="159"/>
-      <c r="H54" s="159"/>
-      <c r="I54" s="159"/>
-      <c r="J54" s="159"/>
-      <c r="K54" s="159"/>
-      <c r="L54" s="159"/>
-      <c r="M54" s="159"/>
-      <c r="N54" s="159"/>
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="167"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="167"/>
+      <c r="L54" s="167"/>
+      <c r="M54" s="167"/>
+      <c r="N54" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="D49:N54"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="N3:O3"/>
@@ -5333,6 +5333,12 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5346,28 +5352,28 @@
   <sheetData>
     <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="181" t="s">
+      <c r="E7" s="182" t="s">
         <v>165</v>
       </c>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="180"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="181"/>
       <c r="L7" s="44"/>
       <c r="M7" s="45"/>
     </row>
     <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="183" t="s">
+      <c r="E8" s="184" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="182"/>
-      <c r="G8" s="182"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="182"/>
-      <c r="K8" s="180"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="181"/>
       <c r="L8" s="46"/>
       <c r="M8" s="47"/>
     </row>
@@ -5411,15 +5417,15 @@
       <c r="M11" s="47"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E12" s="184" t="s">
+      <c r="E12" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="187"/>
       <c r="L12" s="46"/>
       <c r="M12" s="47"/>
     </row>
@@ -5451,10 +5457,10 @@
         <v>45600</v>
       </c>
       <c r="K14" s="47"/>
-      <c r="L14" s="174" t="s">
+      <c r="L14" s="175" t="s">
         <v>173</v>
       </c>
-      <c r="M14" s="175"/>
+      <c r="M14" s="176"/>
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E15" s="46" t="s">
@@ -5480,8 +5486,8 @@
       <c r="I16" s="49"/>
       <c r="J16" s="49"/>
       <c r="K16" s="47"/>
-      <c r="L16" s="176"/>
-      <c r="M16" s="175"/>
+      <c r="L16" s="177"/>
+      <c r="M16" s="176"/>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" s="46"/>
@@ -5517,45 +5523,45 @@
       <c r="M19" s="56"/>
     </row>
     <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="177" t="s">
+      <c r="E20" s="178" t="s">
         <v>175</v>
       </c>
-      <c r="F20" s="178"/>
-      <c r="G20" s="178"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="178"/>
-      <c r="J20" s="179">
+      <c r="F20" s="179"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="179"/>
+      <c r="I20" s="179"/>
+      <c r="J20" s="180">
         <f>PRORRATEO!H12</f>
         <v>131782.53545009997</v>
       </c>
-      <c r="K20" s="180"/>
+      <c r="K20" s="181"/>
       <c r="L20" s="57"/>
       <c r="M20" s="58"/>
     </row>
     <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G25" s="181" t="s">
+      <c r="G25" s="182" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="182"/>
-      <c r="I25" s="182"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="180"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="183"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="183"/>
+      <c r="M25" s="181"/>
       <c r="N25" s="44"/>
       <c r="O25" s="45"/>
     </row>
     <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G26" s="183" t="s">
+      <c r="G26" s="184" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="182"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="180"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="183"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="183"/>
+      <c r="M26" s="181"/>
       <c r="N26" s="46"/>
       <c r="O26" s="47"/>
     </row>
@@ -5599,15 +5605,15 @@
       <c r="O29" s="47"/>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="G30" s="184" t="s">
+      <c r="G30" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="185"/>
-      <c r="M30" s="186"/>
+      <c r="H30" s="186"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="186"/>
+      <c r="K30" s="186"/>
+      <c r="L30" s="186"/>
+      <c r="M30" s="187"/>
       <c r="N30" s="46"/>
       <c r="O30" s="47"/>
     </row>
@@ -5636,10 +5642,10 @@
         <v>45600</v>
       </c>
       <c r="M32" s="47"/>
-      <c r="N32" s="174" t="s">
+      <c r="N32" s="175" t="s">
         <v>173</v>
       </c>
-      <c r="O32" s="175"/>
+      <c r="O32" s="176"/>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="46" t="s">
@@ -5665,8 +5671,8 @@
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
       <c r="M34" s="47"/>
-      <c r="N34" s="176"/>
-      <c r="O34" s="175"/>
+      <c r="N34" s="177"/>
+      <c r="O34" s="176"/>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G35" s="46"/>
@@ -5702,18 +5708,18 @@
       <c r="O37" s="56"/>
     </row>
     <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G38" s="177" t="s">
+      <c r="G38" s="178" t="s">
         <v>175</v>
       </c>
-      <c r="H38" s="178"/>
-      <c r="I38" s="178"/>
-      <c r="J38" s="178"/>
-      <c r="K38" s="178"/>
-      <c r="L38" s="179">
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
+      <c r="J38" s="179"/>
+      <c r="K38" s="179"/>
+      <c r="L38" s="180">
         <f>PRORRATEO!J30</f>
         <v>0</v>
       </c>
-      <c r="M38" s="180"/>
+      <c r="M38" s="181"/>
       <c r="N38" s="57"/>
       <c r="O38" s="58"/>
     </row>
